--- a/Musee_Infinis_clean.xlsx
+++ b/Musee_Infinis_clean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Angel\Projets\Minecraft_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893C6F4C-866D-4FA8-94D9-8E3A43A72152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42867D60-B892-44B6-ACC2-E50297944756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7957,7 +7957,7 @@
     <t>Netherite Upgrade</t>
   </si>
   <si>
-    <t>&amp;</t>
+    <t>Items</t>
   </si>
 </sst>
 </file>
@@ -30923,96 +30923,210 @@
       </c>
     </row>
     <row r="1323" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1323">
+        <v>1</v>
+      </c>
+      <c r="C1323">
+        <v>27</v>
+      </c>
       <c r="G1323" t="s">
         <v>2626</v>
       </c>
     </row>
     <row r="1324" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1324">
+        <v>1</v>
+      </c>
+      <c r="C1324">
+        <v>27</v>
+      </c>
       <c r="G1324" t="s">
         <v>2627</v>
       </c>
     </row>
     <row r="1325" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1325">
+        <v>1</v>
+      </c>
+      <c r="C1325">
+        <v>27</v>
+      </c>
       <c r="G1325" t="s">
         <v>2628</v>
       </c>
     </row>
     <row r="1326" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1326">
+        <v>1</v>
+      </c>
+      <c r="C1326">
+        <v>27</v>
+      </c>
       <c r="G1326" t="s">
         <v>2629</v>
       </c>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1327">
+        <v>1</v>
+      </c>
+      <c r="C1327">
+        <v>27</v>
+      </c>
       <c r="G1327" t="s">
         <v>2630</v>
       </c>
     </row>
     <row r="1328" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1328">
+        <v>1</v>
+      </c>
+      <c r="C1328">
+        <v>27</v>
+      </c>
       <c r="G1328" t="s">
         <v>2631</v>
       </c>
     </row>
-    <row r="1329" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="1329" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1329">
+        <v>1</v>
+      </c>
+      <c r="C1329">
+        <v>27</v>
+      </c>
       <c r="G1329" t="s">
         <v>2632</v>
       </c>
     </row>
-    <row r="1330" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="1330" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1330">
+        <v>1</v>
+      </c>
+      <c r="C1330">
+        <v>27</v>
+      </c>
       <c r="G1330" t="s">
         <v>2633</v>
       </c>
     </row>
-    <row r="1331" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="1331" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1331">
+        <v>1</v>
+      </c>
+      <c r="C1331">
+        <v>27</v>
+      </c>
       <c r="G1331" t="s">
         <v>2634</v>
       </c>
     </row>
-    <row r="1332" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="1332" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1332">
+        <v>1</v>
+      </c>
+      <c r="C1332">
+        <v>27</v>
+      </c>
       <c r="G1332" t="s">
         <v>2635</v>
       </c>
     </row>
-    <row r="1333" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="1333" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1333">
+        <v>1</v>
+      </c>
+      <c r="C1333">
+        <v>27</v>
+      </c>
       <c r="G1333" t="s">
         <v>2636</v>
       </c>
     </row>
-    <row r="1334" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="1334" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1334">
+        <v>1</v>
+      </c>
+      <c r="C1334">
+        <v>27</v>
+      </c>
       <c r="G1334" t="s">
         <v>2637</v>
       </c>
     </row>
-    <row r="1335" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="1335" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1335">
+        <v>1</v>
+      </c>
+      <c r="C1335">
+        <v>27</v>
+      </c>
       <c r="G1335" t="s">
         <v>2638</v>
       </c>
     </row>
-    <row r="1336" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="1336" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1336">
+        <v>1</v>
+      </c>
+      <c r="C1336">
+        <v>27</v>
+      </c>
       <c r="G1336" t="s">
         <v>2639</v>
       </c>
     </row>
-    <row r="1337" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="1337" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1337">
+        <v>1</v>
+      </c>
+      <c r="C1337">
+        <v>27</v>
+      </c>
       <c r="G1337" t="s">
         <v>2640</v>
       </c>
     </row>
-    <row r="1338" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="1338" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1338">
+        <v>1</v>
+      </c>
+      <c r="C1338">
+        <v>27</v>
+      </c>
       <c r="G1338" t="s">
         <v>2641</v>
       </c>
     </row>
-    <row r="1339" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="1339" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1339">
+        <v>1</v>
+      </c>
+      <c r="C1339">
+        <v>27</v>
+      </c>
       <c r="G1339" t="s">
         <v>2642</v>
       </c>
     </row>
-    <row r="1340" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="1340" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1340">
+        <v>1</v>
+      </c>
+      <c r="C1340">
+        <v>27</v>
+      </c>
       <c r="G1340" t="s">
         <v>2643</v>
       </c>
     </row>
-    <row r="1341" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="1341" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1341">
+        <v>64</v>
+      </c>
+      <c r="C1341">
+        <v>1728</v>
+      </c>
       <c r="G1341" t="s">
         <v>2644</v>
       </c>
